--- a/data/processed/unemployment_processed.xlsx
+++ b/data/processed/unemployment_processed.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14117,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16095,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16906,7 +16906,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17445,7 +17445,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17635,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18013,7 +18013,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18141,7 +18141,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18670,7 +18670,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18835,7 +18835,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19000,7 +19000,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19132,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19328,7 @@
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20053,7 +20053,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20210,7 +20210,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20243,7 +20243,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20557,7 +20557,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20714,7 +20714,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20745,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20776,7 +20776,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20931,7 +20931,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21127,7 +21127,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21226,7 +21226,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21292,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21325,7 +21325,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21556,7 +21556,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21713,7 +21713,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21934,7 +21934,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21967,7 +21967,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22188,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22345,7 +22345,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22376,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22566,7 +22566,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22725,7 +22725,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22756,7 +22756,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22849,7 +22849,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -22973,7 +22973,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
@@ -23287,7 +23287,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>2026-07-28 01:30:01</t>
+          <t>2026-07-28 08:51:22</t>
         </is>
       </c>
     </row>
